--- a/data.mn/public/datasets/industrial-production-national.xlsx
+++ b/data.mn/public/datasets/industrial-production-national.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1230,9 +1230,7 @@
       <c r="B33" t="n">
         <v>42863.6</v>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
         <v>4105.9</v>
       </c>
@@ -1256,9 +1254,7 @@
       <c r="B34" t="n">
         <v>28645</v>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
         <v>4667.1</v>
       </c>
@@ -1282,9 +1278,7 @@
       <c r="B35" t="n">
         <v>34708.1</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
         <v>2565.4</v>
       </c>
@@ -1308,9 +1302,7 @@
       <c r="B36" t="n">
         <v>74283.7</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
         <v>4888.9</v>
       </c>
@@ -1334,9 +1326,7 @@
       <c r="B37" t="n">
         <v>95055.8</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
         <v>4188.3</v>
       </c>
@@ -1360,9 +1350,7 @@
       <c r="B38" t="n">
         <v>95540</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
         <v>3775.1</v>
       </c>
@@ -2209,9 +2197,7 @@
       <c r="C33" t="n">
         <v>4105.9</v>
       </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>0</v>
       </c>
@@ -2235,9 +2221,7 @@
       <c r="C34" t="n">
         <v>4667.1</v>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>0</v>
       </c>
@@ -2261,9 +2245,7 @@
       <c r="C35" t="n">
         <v>2565.4</v>
       </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>0</v>
       </c>
@@ -2287,9 +2269,7 @@
       <c r="C36" t="n">
         <v>4888.9</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>0</v>
       </c>
@@ -2313,9 +2293,7 @@
       <c r="C37" t="n">
         <v>4188.3</v>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>0</v>
       </c>
@@ -2339,9 +2317,7 @@
       <c r="C38" t="n">
         <v>3775.1</v>
       </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>0</v>
       </c>
